--- a/diseases/d173/2005-2009.xlsx
+++ b/diseases/d173/2005-2009.xlsx
@@ -3792,11 +3792,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_RIFT_ANNUAL</t>
@@ -3814,12 +3809,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -3829,11 +3819,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3899,17 +3884,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3948,34 +3933,12 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Rift valley fever</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3983,64 +3946,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN24" t="b">
-        <v>1</v>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4048,27 +3953,17 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
         <v>1</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -4076,7 +3971,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -4096,7 +3991,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -4138,12 +4033,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4168,12 +4063,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4187,7 +4082,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
+          <t>SER_BE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4207,7 +4102,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
+          <t>SER_BE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -4220,7 +4115,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -4240,7 +4135,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -4282,12 +4177,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4331,7 +4226,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_DE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4351,7 +4246,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_DE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -4359,42 +4254,42 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4321,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4475,7 +4370,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_EE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4495,7 +4390,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_EE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -4503,42 +4398,42 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4570,12 +4465,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4619,7 +4514,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_ES_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4639,7 +4534,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_ES_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -4652,7 +4547,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4672,7 +4567,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -4714,12 +4609,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4763,7 +4658,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_RIFT_ANNUAL</t>
+          <t>SER_FR_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4783,7 +4678,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_RIFT_ANNUAL</t>
+          <t>SER_FR_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -4796,7 +4691,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -4816,7 +4711,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -4858,12 +4753,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4907,7 +4802,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_RIFT_ANNUAL</t>
+          <t>SER_GB_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4927,7 +4822,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_RIFT_ANNUAL</t>
+          <t>SER_GB_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -4940,7 +4835,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4960,7 +4855,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -5002,12 +4897,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5051,7 +4946,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_RIFT_ANNUAL</t>
+          <t>SER_GR_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5071,7 +4966,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_RIFT_ANNUAL</t>
+          <t>SER_GR_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -5084,7 +4979,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -5104,7 +4999,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -5146,12 +5041,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5195,7 +5090,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_RIFT_ANNUAL</t>
+          <t>SER_HU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5215,7 +5110,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_RIFT_ANNUAL</t>
+          <t>SER_HU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -5228,7 +5123,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -5248,7 +5143,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -5290,12 +5185,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5339,7 +5234,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_IT_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5359,7 +5254,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_IT_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -5372,7 +5267,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -5392,7 +5287,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -5434,12 +5329,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5483,7 +5378,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LT_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5503,7 +5398,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LT_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -5516,7 +5411,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -5536,7 +5431,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -5578,12 +5473,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5627,7 +5522,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5647,7 +5542,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -5660,7 +5555,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -5680,7 +5575,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -5722,12 +5617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5771,7 +5666,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LV_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5791,7 +5686,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LV_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -5804,7 +5699,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -5824,7 +5719,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -5866,12 +5761,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5915,7 +5810,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_RIFT_ANNUAL</t>
+          <t>SER_MT_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5935,7 +5830,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_RIFT_ANNUAL</t>
+          <t>SER_MT_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -5948,7 +5843,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -5968,7 +5863,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -6010,12 +5905,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6059,7 +5954,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_RIFT_ANNUAL</t>
+          <t>SER_NO_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6079,7 +5974,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_RIFT_ANNUAL</t>
+          <t>SER_NO_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -6087,42 +5982,42 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6049,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6203,7 +6098,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_RIFT_ANNUAL</t>
+          <t>SER_PL_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6223,7 +6118,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_RIFT_ANNUAL</t>
+          <t>SER_PL_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6231,42 +6126,42 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6193,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6347,7 +6242,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_RIFT_ANNUAL</t>
+          <t>SER_RO_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6367,7 +6262,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_RIFT_ANNUAL</t>
+          <t>SER_RO_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -6380,7 +6275,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6400,7 +6295,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6442,12 +6337,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6491,7 +6386,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6511,7 +6406,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SE_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -6519,42 +6414,42 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6481,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6635,7 +6530,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6655,7 +6550,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -6663,42 +6558,42 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6625,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6777,14 +6672,9 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6799,27 +6689,17 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
+          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
         <v>1</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -6827,7 +6707,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -6847,7 +6727,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -6856,384 +6736,6 @@
         </is>
       </c>
       <c r="BC43" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>D173</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>rift-valley-fever</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Rift Valley fever</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>D173</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Rift Valley fever</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>裂谷热</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Rift valley fever</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV44" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA44" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB44" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC44" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>D173</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>rift-valley-fever</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Rift Valley fever</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>D173</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Rift Valley fever</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>裂谷热</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP45" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV45" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA45" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC45" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -7365,7 +6867,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -7385,7 +6887,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7395,7 +6897,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
